--- a/配置表格/__beans__.xlsx
+++ b/配置表格/__beans__.xlsx
@@ -1587,8 +1587,10 @@
       <x:c r="G16" s="2" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="H16" s="2" t="s">
-        <x:v>24</x:v>
+      <x:c r="H16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">s</x:t>
+        </x:is>
       </x:c>
       <x:c r="J16" s="2" t="s">
         <x:v>25</x:v>
@@ -1915,16 +1917,6 @@
       <x:c r="H39" s="2" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="J39" s="2" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="L39" s="2" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="M39" s="2"/>
-      <x:c r="N39" s="2" t="s">
-        <x:v>123</x:v>
-      </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="B40" s="2" t="s">
@@ -1942,8 +1934,10 @@
       <x:c r="H40" s="2" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="J40" s="2" t="s">
-        <x:v>127</x:v>
+      <x:c r="J40" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">circle_radius</x:t>
+        </x:is>
       </x:c>
       <x:c r="L40" s="2" t="s">
         <x:v>128</x:v>
@@ -1969,8 +1963,10 @@
       <x:c r="H41" s="2" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="J41" s="2" t="s">
-        <x:v>127</x:v>
+      <x:c r="J41" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">sector_radius</x:t>
+        </x:is>
       </x:c>
       <x:c r="L41" s="2" t="s">
         <x:v>128</x:v>
@@ -2112,8 +2108,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="M49" s="2"/>
-      <x:c r="N49" s="2" t="s">
-        <x:v>156</x:v>
+      <x:c r="N49" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">技能效果延迟触发(毫秒)</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -2156,8 +2154,10 @@
       <x:c r="H52" s="2" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="J52" s="2" t="s">
-        <x:v>11</x:v>
+      <x:c r="J52" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">dmg_type</x:t>
+        </x:is>
       </x:c>
       <x:c r="L52" t="s">
         <x:v>165</x:v>
@@ -2168,8 +2168,10 @@
       </x:c>
     </x:row>
     <x:row r="53">
-      <x:c r="J53" s="2" t="s">
-        <x:v>167</x:v>
+      <x:c r="J53" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">dmg_coefficient</x:t>
+        </x:is>
       </x:c>
       <x:c r="L53" s="2" t="s">
         <x:v>26</x:v>
@@ -2180,8 +2182,10 @@
       </x:c>
     </x:row>
     <x:row r="54">
-      <x:c r="J54" s="2" t="s">
-        <x:v>169</x:v>
+      <x:c r="J54" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">dmg_flat</x:t>
+        </x:is>
       </x:c>
       <x:c r="L54" s="2" t="s">
         <x:v>26</x:v>
@@ -2192,8 +2196,10 @@
       </x:c>
     </x:row>
     <x:row r="55">
-      <x:c r="J55" s="2" t="s">
-        <x:v>171</x:v>
+      <x:c r="J55" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">dmg_can_crit</x:t>
+        </x:is>
       </x:c>
       <x:c r="L55" s="2" t="s">
         <x:v>113</x:v>
@@ -2204,8 +2210,10 @@
       </x:c>
     </x:row>
     <x:row r="56">
-      <x:c r="J56" s="2" t="s">
-        <x:v>173</x:v>
+      <x:c r="J56" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">dmg_crit</x:t>
+        </x:is>
       </x:c>
       <x:c r="L56" s="2" t="s">
         <x:v>26</x:v>
@@ -2243,8 +2251,10 @@
       <x:c r="H58" s="2" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="J58" s="2" t="s">
-        <x:v>25</x:v>
+      <x:c r="J58" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">buff_id</x:t>
+        </x:is>
       </x:c>
       <x:c r="L58" s="2" t="s">
         <x:v>26</x:v>
@@ -2270,8 +2280,10 @@
       <x:c r="H59" s="2" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="J59" s="3" t="s">
-        <x:v>11</x:v>
+      <x:c r="J59" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">heal_type</x:t>
+        </x:is>
       </x:c>
       <x:c r="L59" s="3" t="s">
         <x:v>184</x:v>
@@ -2285,8 +2297,10 @@
       <x:c r="B60" s="2"/>
       <x:c r="C60" s="2"/>
       <x:c r="G60" s="2"/>
-      <x:c r="J60" s="2" t="s">
-        <x:v>167</x:v>
+      <x:c r="J60" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">heal_coefficient</x:t>
+        </x:is>
       </x:c>
       <x:c r="L60" s="2" t="s">
         <x:v>26</x:v>
@@ -2297,8 +2311,10 @@
       </x:c>
     </x:row>
     <x:row r="61">
-      <x:c r="J61" s="2" t="s">
-        <x:v>169</x:v>
+      <x:c r="J61" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">heal_flat</x:t>
+        </x:is>
       </x:c>
       <x:c r="L61" s="2" t="s">
         <x:v>26</x:v>
@@ -2309,8 +2325,10 @@
       </x:c>
     </x:row>
     <x:row r="62">
-      <x:c r="J62" s="2" t="s">
-        <x:v>171</x:v>
+      <x:c r="J62" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">heal_can_crit</x:t>
+        </x:is>
       </x:c>
       <x:c r="L62" s="2" t="s">
         <x:v>113</x:v>
@@ -2321,8 +2339,10 @@
       </x:c>
     </x:row>
     <x:row r="63">
-      <x:c r="J63" s="2" t="s">
-        <x:v>173</x:v>
+      <x:c r="J63" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">heal_crit</x:t>
+        </x:is>
       </x:c>
       <x:c r="L63" s="2" t="s">
         <x:v>26</x:v>
@@ -2348,861 +2368,896 @@
       <x:c r="H64" s="2" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="J64" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="L64" s="2" t="s">
-        <x:v>191</x:v>
+      <x:c r="J64" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">summon_id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L64" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
       </x:c>
       <x:c r="M64" s="2"/>
-      <x:c r="N64" s="2" t="s">
-        <x:v>192</x:v>
+      <x:c r="N64" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">从属实体 owned_entity_config.config_id</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="J65" s="2" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="L65" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="L65" s="3" t="s">
+        <x:v>195</x:v>
       </x:c>
       <x:c r="M65" s="2"/>
       <x:c r="N65" s="2" t="s">
-        <x:v>193</x:v>
+        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
-      <x:c r="J66" s="2" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="L66" s="3" t="s">
-        <x:v>195</x:v>
+      <x:c r="J66" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="L66" s="2" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="M66" s="2"/>
-      <x:c r="N66" s="2" t="s">
-        <x:v>196</x:v>
+      <x:c r="N66" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">召唤物持续时间(毫秒)，0=不限</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="67">
-      <x:c r="J67" t="s">
-        <x:v>197</x:v>
+      <x:c r="J67" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">summon_count</x:t>
+        </x:is>
       </x:c>
       <x:c r="L67" s="2" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="M67" s="2"/>
       <x:c r="N67" s="2" t="s">
-        <x:v>198</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="J68" s="2" t="s">
-        <x:v>60</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="L68" s="2" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="M68" s="2"/>
       <x:c r="N68" s="2" t="s">
-        <x:v>199</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="J69" s="2" t="s">
-        <x:v>200</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="L69" s="2" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="M69" s="2"/>
       <x:c r="N69" s="2" t="s">
-        <x:v>201</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="J70" s="2" t="s">
-        <x:v>202</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="L70" s="2" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="M70" s="2"/>
       <x:c r="N70" s="2" t="s">
-        <x:v>203</x:v>
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
+      <x:c r="B71" s="2" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="C71" s="2" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="F71" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="G71" s="2" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="H71" s="2" t="s">
+        <x:v>45</x:v>
+      </x:c>
       <x:c r="J71" s="2" t="s">
-        <x:v>204</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="L71" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="M71" s="2"/>
       <x:c r="N71" s="2" t="s">
-        <x:v>205</x:v>
+        <x:v>211</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
-      <x:c r="B72" s="2" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="C72" s="2" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="F72" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="G72" s="2" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="H72" s="2" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="J72" s="2" t="s">
-        <x:v>209</x:v>
+      <x:c r="B72" s="2"/>
+      <x:c r="C72" s="2"/>
+      <x:c r="G72" s="2"/>
+      <x:c r="H72" s="2"/>
+      <x:c r="J72" t="s">
+        <x:v>212</x:v>
       </x:c>
       <x:c r="L72" s="2" t="s">
-        <x:v>210</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="M72" s="2"/>
       <x:c r="N72" s="2" t="s">
-        <x:v>211</x:v>
+        <x:v>213</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
-      <x:c r="B73" s="2"/>
-      <x:c r="C73" s="2"/>
-      <x:c r="G73" s="2"/>
-      <x:c r="H73" s="2"/>
-      <x:c r="J73" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="L73" s="2" t="s">
-        <x:v>26</x:v>
+      <x:c r="J73" s="2" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="L73" s="3" t="s">
+        <x:v>215</x:v>
       </x:c>
       <x:c r="M73" s="2"/>
       <x:c r="N73" s="2" t="s">
-        <x:v>213</x:v>
+        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="J74" s="2" t="s">
-        <x:v>214</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="L74" s="3" t="s">
-        <x:v>215</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="M74" s="2"/>
       <x:c r="N74" s="2" t="s">
-        <x:v>216</x:v>
+        <x:v>219</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="J75" s="2" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="L75" s="3" t="s">
-        <x:v>218</x:v>
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="L75" s="2" t="s">
+        <x:v>113</x:v>
       </x:c>
       <x:c r="M75" s="2"/>
       <x:c r="N75" s="2" t="s">
-        <x:v>219</x:v>
+        <x:v>221</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
-      <x:c r="J76" s="2" t="s">
-        <x:v>220</x:v>
+      <x:c r="J76" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">move_speed</x:t>
+        </x:is>
       </x:c>
       <x:c r="L76" s="2" t="s">
-        <x:v>113</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="M76" s="2"/>
       <x:c r="N76" s="2" t="s">
-        <x:v>221</x:v>
+        <x:v>223</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
+      <x:c r="B77" s="2" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="C77" s="2" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="F77" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="G77" s="2" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="H77" s="2" t="s">
+        <x:v>45</x:v>
+      </x:c>
       <x:c r="J77" s="2" t="s">
-        <x:v>222</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="L77" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="M77" s="2"/>
       <x:c r="N77" s="2" t="s">
-        <x:v>223</x:v>
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
-      <x:c r="B78" s="2" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="C78" s="2" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="F78" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="G78" s="2" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="H78" s="2" t="s">
-        <x:v>45</x:v>
-      </x:c>
+      <x:c r="B78" s="2"/>
+      <x:c r="C78" s="2"/>
+      <x:c r="G78" s="2"/>
       <x:c r="J78" s="2" t="s">
-        <x:v>227</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="L78" s="2" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="M78" s="2"/>
       <x:c r="N78" s="2" t="s">
-        <x:v>228</x:v>
+        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="B79" s="2"/>
       <x:c r="C79" s="2"/>
       <x:c r="G79" s="2"/>
-      <x:c r="J79" s="2" t="s">
-        <x:v>229</x:v>
+      <x:c r="J79" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">proj_speed</x:t>
+        </x:is>
       </x:c>
       <x:c r="L79" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="M79" s="2"/>
       <x:c r="N79" s="2" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
-      <x:c r="B80" s="2"/>
-      <x:c r="C80" s="2"/>
-      <x:c r="G80" s="2"/>
       <x:c r="J80" s="2" t="s">
-        <x:v>222</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="L80" s="2" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="M80" s="2"/>
       <x:c r="N80" s="2" t="s">
-        <x:v>231</x:v>
+        <x:v>233</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="J81" s="2" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="L81" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="L81" s="3" t="s">
+        <x:v>235</x:v>
       </x:c>
       <x:c r="M81" s="2"/>
       <x:c r="N81" s="2" t="s">
-        <x:v>233</x:v>
+        <x:v>236</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
-      <x:c r="J82" s="2" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="L82" s="3" t="s">
-        <x:v>235</x:v>
+      <x:c r="J82" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">proj_count</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L82" s="2" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="M82" s="2"/>
       <x:c r="N82" s="2" t="s">
-        <x:v>236</x:v>
+        <x:v>237</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="J83" s="2" t="s">
-        <x:v>60</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="L83" s="2" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="M83" s="2"/>
-      <x:c r="N83" s="2" t="s">
-        <x:v>237</x:v>
+      <x:c r="N83" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">投射物发射波次间隔(毫秒)</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="J84" s="2" t="s">
-        <x:v>238</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L84" s="2" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="M84" s="2"/>
       <x:c r="N84" s="2" t="s">
-        <x:v>239</x:v>
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="J85" s="2" t="s">
-        <x:v>240</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="L85" s="2" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="M85" s="2"/>
       <x:c r="N85" s="2" t="s">
-        <x:v>241</x:v>
+        <x:v>243</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="J86" s="2" t="s">
-        <x:v>242</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="L86" s="2" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="M86" s="2"/>
       <x:c r="N86" s="2" t="s">
-        <x:v>243</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
       <x:c r="J87" s="2" t="s">
-        <x:v>244</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="L87" s="2" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="M87" s="2"/>
       <x:c r="N87" s="2" t="s">
-        <x:v>245</x:v>
+        <x:v>247</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="J88" s="2" t="s">
-        <x:v>246</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="L88" s="2" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="M88" s="2"/>
       <x:c r="N88" s="2" t="s">
-        <x:v>247</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
-      <x:c r="J89" s="2" t="s">
-        <x:v>248</x:v>
+      <x:c r="J89" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">proj_sub_skill_id</x:t>
+        </x:is>
       </x:c>
       <x:c r="L89" s="2" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="M89" s="2"/>
       <x:c r="N89" s="2" t="s">
-        <x:v>249</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
-      <x:c r="J90" s="2" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="L90" s="2" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="M90" s="2"/>
-      <x:c r="N90" s="2" t="s">
-        <x:v>251</x:v>
+      <x:c r="J90" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">seek_distance</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L90" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M90" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">c,a</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N90" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">追踪·外飞距离（码）：出膛后先沿发射方向直飞这么远，才开始索敌转向；0=出膛即索敌。仅运行轨迹=追踪时生效</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="91">
-      <x:c r="B91" s="2" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="C91" s="2" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="F91" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="G91" s="2" t="s">
-        <x:v>254</x:v>
-      </x:c>
-      <x:c r="H91" s="2" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="J91" s="2" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="L91" s="2" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="M91" s="2"/>
-      <x:c r="N91" s="2" t="s">
-        <x:v>255</x:v>
+      <x:c r="J91" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">seek_radius</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L91" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M91" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">c,a</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N91" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">追踪·索敌半径（码）：以弹体当前位置为圆心找目标的范围，运行轨迹=追踪时必须 &gt;0</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="92">
-      <x:c r="B92" s="2"/>
-      <x:c r="G92" s="2"/>
-      <x:c r="J92" s="2"/>
-      <x:c r="L92" s="2"/>
-      <x:c r="M92" s="2"/>
-      <x:c r="N92" s="2"/>
+      <x:c r="J92" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">turn_rate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L92" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M92" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">c,a</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N92" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">追踪·最大转向速度（度/秒）：越小转弯越大、越像导弹；0=不限，每次校正直接对准目标。仅运行轨迹=追踪时生效</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="93">
-      <x:c r="B93" s="2" t="s">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="G93" s="2" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="H93" s="2" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="J93" s="2" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="L93" s="2" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="M93" s="2"/>
-      <x:c r="N93" s="2" t="s">
-        <x:v>257</x:v>
+      <x:c r="J93" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">seek_mode</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L93" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ProjectileSeekMode</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M93" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">c,a</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N93" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">追踪·目标分配：同一次发射的多枚弹体怎么分目标，默认=最近。仅运行轨迹=追踪时生效</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="94">
       <x:c r="B94" s="2" t="s">
-        <x:v>258</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C94" s="2" t="s">
-        <x:v>256</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="F94" t="s">
-        <x:v>259</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="G94" s="2" t="s">
-        <x:v>260</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="H94" s="2" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="J94" s="2" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="L94" s="3" t="s">
-        <x:v>262</x:v>
+      <x:c r="J94" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">call_skill_id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L94" s="2" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="M94" s="2"/>
       <x:c r="N94" s="2" t="s">
-        <x:v>263</x:v>
+        <x:v>255</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
-      <x:c r="B95" s="2" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="C95" s="2" t="s">
+      <x:c r="B95" s="2"/>
+      <x:c r="G95" s="2"/>
+      <x:c r="J95" s="2"/>
+      <x:c r="L95" s="2"/>
+      <x:c r="M95" s="2"/>
+      <x:c r="N95" s="2"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="B96" s="2" t="s">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="F95" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="G95" s="2" t="s">
-        <x:v>266</x:v>
-      </x:c>
-      <x:c r="H95" s="2" t="s">
+      <x:c r="G96" s="2" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="H96" s="2" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="J95" s="2" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="L95" s="3" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="M95" s="2"/>
-      <x:c r="N95" s="2" t="s">
-        <x:v>166</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="96">
       <x:c r="J96" s="2" t="s">
-        <x:v>167</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="L96" s="2" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="M96" s="2"/>
       <x:c r="N96" s="2" t="s">
-        <x:v>168</x:v>
+        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
+      <x:c r="B97" s="2" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="C97" s="2" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F97" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="G97" s="2" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="H97" s="2" t="s">
+        <x:v>45</x:v>
+      </x:c>
       <x:c r="J97" s="2" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="L97" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="L97" s="3" t="s">
+        <x:v>262</x:v>
       </x:c>
       <x:c r="M97" s="2"/>
       <x:c r="N97" s="2" t="s">
-        <x:v>170</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
+      <x:c r="B98" s="2" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="C98" s="2" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F98" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="G98" s="2" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="H98" s="2" t="s">
+        <x:v>45</x:v>
+      </x:c>
       <x:c r="J98" s="2" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="L98" s="2" t="s">
-        <x:v>113</x:v>
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="L98" s="3" t="s">
+        <x:v>165</x:v>
       </x:c>
       <x:c r="M98" s="2"/>
       <x:c r="N98" s="2" t="s">
-        <x:v>172</x:v>
+        <x:v>166</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
-      <x:c r="J99" s="2" t="s">
-        <x:v>173</x:v>
+      <x:c r="J99" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">dot_coefficient</x:t>
+        </x:is>
       </x:c>
       <x:c r="L99" s="2" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="M99" s="2"/>
       <x:c r="N99" s="2" t="s">
-        <x:v>174</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
-      <x:c r="B100" s="2" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="C100" s="2" t="s">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="F100" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="G100" s="2" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="H100" s="2" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="J100" s="3" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="L100" s="3" t="s">
-        <x:v>184</x:v>
+      <x:c r="J100" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">dot_flat</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L100" s="2" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="M100" s="2"/>
       <x:c r="N100" s="2" t="s">
-        <x:v>185</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
-      <x:c r="J101" s="2" t="s">
-        <x:v>167</x:v>
+      <x:c r="J101" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">dot_can_crit</x:t>
+        </x:is>
       </x:c>
       <x:c r="L101" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="M101" s="2"/>
       <x:c r="N101" s="2" t="s">
-        <x:v>186</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
-      <x:c r="J102" s="2" t="s">
-        <x:v>169</x:v>
+      <x:c r="J102" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">dot_crit</x:t>
+        </x:is>
       </x:c>
       <x:c r="L102" s="2" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="M102" s="2"/>
       <x:c r="N102" s="2" t="s">
-        <x:v>187</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
-      <x:c r="J103" s="2" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="L103" s="2" t="s">
-        <x:v>113</x:v>
+      <x:c r="B103" s="2" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="C103" s="2" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F103" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="G103" s="2" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="H103" s="2" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="J103" s="3" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="L103" s="3" t="s">
+        <x:v>184</x:v>
       </x:c>
       <x:c r="M103" s="2"/>
       <x:c r="N103" s="2" t="s">
-        <x:v>172</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
-      <x:c r="J104" s="2" t="s">
-        <x:v>173</x:v>
+      <x:c r="J104" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">hot_coefficient</x:t>
+        </x:is>
       </x:c>
       <x:c r="L104" s="2" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="M104" s="2"/>
       <x:c r="N104" s="2" t="s">
-        <x:v>174</x:v>
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
-      <x:c r="B105" s="2" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="C105" s="2" t="s">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="F105" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="G105" s="2" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="H105" s="2" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="J105" s="2" t="s">
-        <x:v>71</x:v>
+      <x:c r="J105" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">hot_flat</x:t>
+        </x:is>
       </x:c>
       <x:c r="L105" s="2" t="s">
-        <x:v>47</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="M105" s="2"/>
       <x:c r="N105" s="2" t="s">
-        <x:v>275</x:v>
+        <x:v>187</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
-      <x:c r="B106" s="2"/>
-      <x:c r="C106" s="2"/>
-      <x:c r="G106" s="2"/>
-      <x:c r="J106" s="2" t="s">
-        <x:v>73</x:v>
+      <x:c r="J106" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">hot_can_crit</x:t>
+        </x:is>
       </x:c>
       <x:c r="L106" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="M106" s="2"/>
       <x:c r="N106" s="2" t="s">
-        <x:v>276</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
-      <x:c r="B107" s="2" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="C107" s="2" t="s">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="F107" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="G107" s="2" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="H107" s="2" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="J107" s="2" t="s">
-        <x:v>250</x:v>
+      <x:c r="J107" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">hot_crit</x:t>
+        </x:is>
       </x:c>
       <x:c r="L107" s="2" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="M107" s="2"/>
       <x:c r="N107" s="2" t="s">
-        <x:v>280</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
-      <x:c r="B108" t="s">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c r="C108"/>
-      <x:c r="D108"/>
-      <x:c r="E108"/>
-      <x:c r="F108"/>
-      <x:c r="G108" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="H108" t="s">
+      <x:c r="B108" s="2" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="C108" s="2" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F108" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="G108" s="2" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="H108" s="2" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="I108"/>
       <x:c r="J108" s="2" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="K108"/>
+        <x:v>71</x:v>
+      </x:c>
       <x:c r="L108" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="M108" s="2"/>
       <x:c r="N108" s="2" t="s">
-        <x:v>284</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
-      <x:c r="B109"/>
-      <x:c r="C109"/>
-      <x:c r="D109"/>
-      <x:c r="E109"/>
-      <x:c r="F109"/>
-      <x:c r="G109"/>
-      <x:c r="H109"/>
-      <x:c r="I109"/>
+      <x:c r="B109" s="2"/>
+      <x:c r="C109" s="2"/>
+      <x:c r="G109" s="2"/>
       <x:c r="J109" s="2" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="K109"/>
+        <x:v>73</x:v>
+      </x:c>
       <x:c r="L109" s="2" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="M109" s="2"/>
       <x:c r="N109" s="2" t="s">
-        <x:v>285</x:v>
+        <x:v>276</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
-      <x:c r="B110" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="C110"/>
-      <x:c r="D110"/>
-      <x:c r="E110"/>
-      <x:c r="F110"/>
-      <x:c r="G110" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="H110" t="s">
+      <x:c r="B110" s="2" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="C110" s="2" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F110" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="G110" s="2" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="H110" s="2" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="I110"/>
-      <x:c r="J110" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="K110"/>
-      <x:c r="L110" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="M110"/>
-      <x:c r="N110" t="s">
-        <x:v>289</x:v>
+      <x:c r="J110" s="2" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="L110" s="2" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="M110" s="2"/>
+      <x:c r="N110" s="2" t="s">
+        <x:v>280</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
-      <x:c r="B111"/>
-      <x:c r="C111"/>
-      <x:c r="D111"/>
-      <x:c r="E111"/>
-      <x:c r="F111"/>
-      <x:c r="G111"/>
-      <x:c r="H111"/>
-      <x:c r="I111"/>
-      <x:c r="J111" t="s">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c r="K111"/>
-      <x:c r="L111" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="M111"/>
-      <x:c r="N111" t="s">
-        <x:v>291</x:v>
+      <x:c r="J111" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">per_target_interval_ms</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L111" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N111" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">同一目标再触发间隔(毫秒)：0=每跳都打；正数=同一目标至少隔这么久再打；-1=同一目标只生效一次</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="112">
-      <x:c r="B112"/>
+      <x:c r="B112" t="s">
+        <x:v>281</x:v>
+      </x:c>
       <x:c r="C112"/>
       <x:c r="D112"/>
       <x:c r="E112"/>
       <x:c r="F112"/>
-      <x:c r="G112"/>
-      <x:c r="H112"/>
+      <x:c r="G112" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="H112" t="s">
+        <x:v>45</x:v>
+      </x:c>
       <x:c r="I112"/>
-      <x:c r="J112" t="s">
-        <x:v>49</x:v>
+      <x:c r="J112" s="2" t="s">
+        <x:v>283</x:v>
       </x:c>
       <x:c r="K112"/>
-      <x:c r="L112" t="s">
-        <x:v>292</x:v>
-      </x:c>
-      <x:c r="M112"/>
-      <x:c r="N112" t="s">
-        <x:v>293</x:v>
+      <x:c r="L112" s="2" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="M112" s="2"/>
+      <x:c r="N112" s="2" t="s">
+        <x:v>284</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
-      <x:c r="B113" t="s">
-        <x:v>294</x:v>
-      </x:c>
+      <x:c r="B113"/>
       <x:c r="C113"/>
       <x:c r="D113"/>
       <x:c r="E113"/>
       <x:c r="F113"/>
-      <x:c r="G113" t="s">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="H113" t="s">
-        <x:v>45</x:v>
-      </x:c>
+      <x:c r="G113"/>
+      <x:c r="H113"/>
       <x:c r="I113"/>
-      <x:c r="J113" t="s">
-        <x:v>71</x:v>
+      <x:c r="J113" s="2" t="s">
+        <x:v>60</x:v>
       </x:c>
       <x:c r="K113"/>
-      <x:c r="L113" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="M113"/>
-      <x:c r="N113" t="s">
-        <x:v>296</x:v>
+      <x:c r="L113" s="2" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="M113" s="2"/>
+      <x:c r="N113" s="2" t="s">
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
-      <x:c r="B114"/>
+      <x:c r="B114" t="s">
+        <x:v>286</x:v>
+      </x:c>
       <x:c r="C114"/>
       <x:c r="D114"/>
       <x:c r="E114"/>
       <x:c r="F114"/>
-      <x:c r="G114"/>
-      <x:c r="H114"/>
+      <x:c r="G114" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="H114" t="s">
+        <x:v>45</x:v>
+      </x:c>
       <x:c r="I114"/>
       <x:c r="J114" t="s">
-        <x:v>153</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="K114"/>
       <x:c r="L114" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="M114"/>
       <x:c r="N114" t="s">
-        <x:v>297</x:v>
+        <x:v>289</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
-      <x:c r="B115" t="s">
-        <x:v>298</x:v>
-      </x:c>
+      <x:c r="B115"/>
       <x:c r="C115"/>
       <x:c r="D115"/>
       <x:c r="E115"/>
       <x:c r="F115"/>
-      <x:c r="G115" t="s">
-        <x:v>299</x:v>
-      </x:c>
-      <x:c r="H115" t="s">
-        <x:v>45</x:v>
-      </x:c>
+      <x:c r="G115"/>
+      <x:c r="H115"/>
       <x:c r="I115"/>
       <x:c r="J115" t="s">
-        <x:v>300</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="K115"/>
       <x:c r="L115" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="M115"/>
       <x:c r="N115" t="s">
-        <x:v>301</x:v>
+        <x:v>291</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
@@ -3215,36 +3270,42 @@
       <x:c r="H116"/>
       <x:c r="I116"/>
       <x:c r="J116" t="s">
-        <x:v>71</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K116"/>
       <x:c r="L116" t="s">
-        <x:v>302</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="M116"/>
       <x:c r="N116" t="s">
-        <x:v>303</x:v>
+        <x:v>293</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
-      <x:c r="B117"/>
+      <x:c r="B117" t="s">
+        <x:v>294</x:v>
+      </x:c>
       <x:c r="C117"/>
       <x:c r="D117"/>
       <x:c r="E117"/>
       <x:c r="F117"/>
-      <x:c r="G117"/>
-      <x:c r="H117"/>
+      <x:c r="G117" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="H117" t="s">
+        <x:v>45</x:v>
+      </x:c>
       <x:c r="I117"/>
       <x:c r="J117" t="s">
-        <x:v>304</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="K117"/>
       <x:c r="L117" t="s">
-        <x:v>292</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="M117"/>
       <x:c r="N117" t="s">
-        <x:v>305</x:v>
+        <x:v>296</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -3257,36 +3318,42 @@
       <x:c r="H118"/>
       <x:c r="I118"/>
       <x:c r="J118" t="s">
-        <x:v>54</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="K118"/>
       <x:c r="L118" t="s">
-        <x:v>306</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="M118"/>
       <x:c r="N118" t="s">
-        <x:v>307</x:v>
+        <x:v>297</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
-      <x:c r="B119"/>
+      <x:c r="B119" t="s">
+        <x:v>298</x:v>
+      </x:c>
       <x:c r="C119"/>
       <x:c r="D119"/>
       <x:c r="E119"/>
       <x:c r="F119"/>
-      <x:c r="G119"/>
-      <x:c r="H119"/>
+      <x:c r="G119" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="H119" t="s">
+        <x:v>45</x:v>
+      </x:c>
       <x:c r="I119"/>
       <x:c r="J119" t="s">
-        <x:v>49</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="K119"/>
       <x:c r="L119" t="s">
-        <x:v>292</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="M119"/>
       <x:c r="N119" t="s">
-        <x:v>308</x:v>
+        <x:v>301</x:v>
       </x:c>
     </x:row>
     <x:row r="120">
@@ -3299,42 +3366,36 @@
       <x:c r="H120"/>
       <x:c r="I120"/>
       <x:c r="J120" t="s">
-        <x:v>309</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="K120"/>
       <x:c r="L120" t="s">
-        <x:v>28</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="M120"/>
       <x:c r="N120" t="s">
-        <x:v>310</x:v>
+        <x:v>303</x:v>
       </x:c>
     </x:row>
     <x:row r="121">
-      <x:c r="B121" t="s">
-        <x:v>311</x:v>
-      </x:c>
+      <x:c r="B121"/>
       <x:c r="C121"/>
       <x:c r="D121"/>
       <x:c r="E121"/>
       <x:c r="F121"/>
-      <x:c r="G121" t="s">
-        <x:v>312</x:v>
-      </x:c>
-      <x:c r="H121" t="s">
-        <x:v>45</x:v>
-      </x:c>
+      <x:c r="G121"/>
+      <x:c r="H121"/>
       <x:c r="I121"/>
       <x:c r="J121" t="s">
-        <x:v>71</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="K121"/>
       <x:c r="L121" t="s">
-        <x:v>302</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="M121"/>
       <x:c r="N121" t="s">
-        <x:v>313</x:v>
+        <x:v>305</x:v>
       </x:c>
     </x:row>
     <x:row r="122">
@@ -3347,15 +3408,15 @@
       <x:c r="H122"/>
       <x:c r="I122"/>
       <x:c r="J122" t="s">
-        <x:v>304</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K122"/>
       <x:c r="L122" t="s">
-        <x:v>292</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="M122"/>
       <x:c r="N122" t="s">
-        <x:v>305</x:v>
+        <x:v>307</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
@@ -3368,15 +3429,15 @@
       <x:c r="H123"/>
       <x:c r="I123"/>
       <x:c r="J123" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K123"/>
       <x:c r="L123" t="s">
-        <x:v>306</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="M123"/>
       <x:c r="N123" t="s">
-        <x:v>307</x:v>
+        <x:v>308</x:v>
       </x:c>
     </x:row>
     <x:row r="124">
@@ -3389,343 +3450,306 @@
       <x:c r="H124"/>
       <x:c r="I124"/>
       <x:c r="J124" t="s">
-        <x:v>49</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="K124"/>
       <x:c r="L124" t="s">
-        <x:v>292</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="M124"/>
       <x:c r="N124" t="s">
-        <x:v>308</x:v>
+        <x:v>310</x:v>
       </x:c>
     </x:row>
     <x:row r="125">
-      <x:c r="B125"/>
+      <x:c r="B125" t="s">
+        <x:v>311</x:v>
+      </x:c>
       <x:c r="C125"/>
       <x:c r="D125"/>
       <x:c r="E125"/>
       <x:c r="F125"/>
-      <x:c r="G125"/>
-      <x:c r="H125"/>
+      <x:c r="G125" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="H125" t="s">
+        <x:v>45</x:v>
+      </x:c>
       <x:c r="I125"/>
       <x:c r="J125" t="s">
-        <x:v>309</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="K125"/>
       <x:c r="L125" t="s">
-        <x:v>28</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="M125"/>
       <x:c r="N125" t="s">
-        <x:v>310</x:v>
+        <x:v>313</x:v>
       </x:c>
     </x:row>
     <x:row r="126">
-      <x:c r="B126" s="2" t="s">
-        <x:v>314</x:v>
-      </x:c>
-      <x:c r="G126" t="s">
-        <x:v>315</x:v>
-      </x:c>
-      <x:c r="H126" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="J126" s="3" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="L126" s="8" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="N126" s="3" t="s">
-        <x:v>316</x:v>
+      <x:c r="B126"/>
+      <x:c r="C126"/>
+      <x:c r="D126"/>
+      <x:c r="E126"/>
+      <x:c r="F126"/>
+      <x:c r="G126"/>
+      <x:c r="H126"/>
+      <x:c r="I126"/>
+      <x:c r="J126" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="K126"/>
+      <x:c r="L126" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="M126"/>
+      <x:c r="N126" t="s">
+        <x:v>305</x:v>
       </x:c>
     </x:row>
     <x:row r="127">
-      <x:c r="B127" t="s">
-        <x:v>317</x:v>
-      </x:c>
-      <x:c r="C127" t="s">
-        <x:v>314</x:v>
-      </x:c>
-      <x:c r="F127" t="s">
-        <x:v>318</x:v>
-      </x:c>
-      <x:c r="G127" t="s">
-        <x:v>319</x:v>
-      </x:c>
-      <x:c r="H127" t="s">
-        <x:v>45</x:v>
-      </x:c>
+      <x:c r="B127"/>
+      <x:c r="C127"/>
+      <x:c r="D127"/>
+      <x:c r="E127"/>
+      <x:c r="F127"/>
+      <x:c r="G127"/>
+      <x:c r="H127"/>
+      <x:c r="I127"/>
       <x:c r="J127" t="s">
-        <x:v>320</x:v>
-      </x:c>
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="K127"/>
       <x:c r="L127" t="s">
-        <x:v>47</x:v>
-      </x:c>
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="M127"/>
       <x:c r="N127" t="s">
-        <x:v>321</x:v>
+        <x:v>307</x:v>
       </x:c>
     </x:row>
     <x:row r="128">
+      <x:c r="B128"/>
+      <x:c r="C128"/>
+      <x:c r="D128"/>
+      <x:c r="E128"/>
+      <x:c r="F128"/>
+      <x:c r="G128"/>
+      <x:c r="H128"/>
+      <x:c r="I128"/>
       <x:c r="J128" t="s">
         <x:v>49</x:v>
       </x:c>
+      <x:c r="K128"/>
       <x:c r="L128" t="s">
-        <x:v>26</x:v>
-      </x:c>
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="M128"/>
       <x:c r="N128" t="s">
-        <x:v>322</x:v>
+        <x:v>308</x:v>
       </x:c>
     </x:row>
     <x:row r="129">
-      <x:c r="B129" t="s">
-        <x:v>323</x:v>
-      </x:c>
-      <x:c r="C129" t="s">
+      <x:c r="B129"/>
+      <x:c r="C129"/>
+      <x:c r="D129"/>
+      <x:c r="E129"/>
+      <x:c r="F129"/>
+      <x:c r="G129"/>
+      <x:c r="H129"/>
+      <x:c r="I129"/>
+      <x:c r="J129" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="K129"/>
+      <x:c r="L129" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="M129"/>
+      <x:c r="N129" t="s">
+        <x:v>310</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130">
+      <x:c r="B130" s="2" t="s">
         <x:v>314</x:v>
       </x:c>
-      <x:c r="F129" t="s">
-        <x:v>324</x:v>
-      </x:c>
-      <x:c r="G129" t="s">
-        <x:v>325</x:v>
-      </x:c>
-      <x:c r="H129" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="J129" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="L129" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="N129" t="s">
-        <x:v>326</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="130">
-      <x:c r="B130" t="s">
-        <x:v>327</x:v>
-      </x:c>
-      <x:c r="C130" t="s">
-        <x:v>314</x:v>
-      </x:c>
-      <x:c r="F130" t="s">
-        <x:v>328</x:v>
-      </x:c>
       <x:c r="G130" t="s">
-        <x:v>329</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="H130" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="J130" t="s">
-        <x:v>330</x:v>
-      </x:c>
-      <x:c r="L130" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="N130" t="s">
-        <x:v>331</x:v>
-      </x:c>
     </x:row>
     <x:row r="131">
       <x:c r="B131" t="s">
-        <x:v>332</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="C131" t="s">
         <x:v>314</x:v>
       </x:c>
       <x:c r="F131" t="s">
-        <x:v>333</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="G131" t="s">
-        <x:v>334</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="H131" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="J131" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="L131" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N131" t="s">
+        <x:v>321</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132">
+      <x:c r="J132" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="L132" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="N132" t="s">
+        <x:v>322</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133">
+      <x:c r="B133" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="C133" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="F133" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="G133" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="H133" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="J133" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="L133" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="N133" t="s">
+        <x:v>326</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134">
+      <x:c r="B134" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="C134" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="F134" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="G134" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="H134" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="J134" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="L134" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="N134" t="s">
+        <x:v>331</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135">
+      <x:c r="B135" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="C135" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="F135" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="G135" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="H135" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="J135" t="s">
         <x:v>335</x:v>
       </x:c>
-      <x:c r="L131" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="N131" t="s">
+      <x:c r="L135" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="N135" t="s">
         <x:v>336</x:v>
       </x:c>
-    </x:row>
-    <x:row r="132">
-      <x:c r="A132"/>
-      <x:c r="B132" t="str">
-        <x:v>AffixMod</x:v>
-      </x:c>
-      <x:c r="C132"/>
-      <x:c r="D132"/>
-      <x:c r="E132"/>
-      <x:c r="F132"/>
-      <x:c r="G132" t="str">
-        <x:v>词条修改基类；无公共参数</x:v>
-      </x:c>
-      <x:c r="H132" t="str">
-        <x:v>a</x:v>
-      </x:c>
-      <x:c r="I132"/>
-      <x:c r="J132"/>
-      <x:c r="K132"/>
-      <x:c r="L132"/>
-      <x:c r="M132"/>
-      <x:c r="N132"/>
-      <x:c r="O132"/>
-      <x:c r="P132"/>
-    </x:row>
-    <x:row r="133">
-      <x:c r="A133"/>
-      <x:c r="B133" t="str">
-        <x:v>AffixBaseParamMod</x:v>
-      </x:c>
-      <x:c r="C133" t="str">
-        <x:v>AffixMod</x:v>
-      </x:c>
-      <x:c r="D133"/>
-      <x:c r="E133"/>
-      <x:c r="F133" t="str">
-        <x:v>修改_基础参数</x:v>
-      </x:c>
-      <x:c r="G133" t="str">
-        <x:v>修改技能基础数值</x:v>
-      </x:c>
-      <x:c r="H133" t="str">
-        <x:v>a</x:v>
-      </x:c>
-      <x:c r="I133"/>
-      <x:c r="J133" t="str">
-        <x:v>param</x:v>
-      </x:c>
-      <x:c r="K133"/>
-      <x:c r="L133" t="str">
-        <x:v>AffixBaseParam</x:v>
-      </x:c>
-      <x:c r="M133"/>
-      <x:c r="N133" t="str">
-        <x:v>基础参数</x:v>
-      </x:c>
-      <x:c r="O133"/>
-      <x:c r="P133"/>
-    </x:row>
-    <x:row r="134">
-      <x:c r="A134"/>
-      <x:c r="B134"/>
-      <x:c r="C134"/>
-      <x:c r="D134"/>
-      <x:c r="E134"/>
-      <x:c r="F134"/>
-      <x:c r="G134"/>
-      <x:c r="H134"/>
-      <x:c r="I134"/>
-      <x:c r="J134" t="str">
-        <x:v>op</x:v>
-      </x:c>
-      <x:c r="K134"/>
-      <x:c r="L134" t="str">
-        <x:v>AffixModifyOp</x:v>
-      </x:c>
-      <x:c r="M134"/>
-      <x:c r="N134" t="str">
-        <x:v>修改方式</x:v>
-      </x:c>
-      <x:c r="O134"/>
-      <x:c r="P134"/>
-    </x:row>
-    <x:row r="135">
-      <x:c r="A135"/>
-      <x:c r="B135"/>
-      <x:c r="C135"/>
-      <x:c r="D135"/>
-      <x:c r="E135"/>
-      <x:c r="F135"/>
-      <x:c r="G135"/>
-      <x:c r="H135"/>
-      <x:c r="I135"/>
-      <x:c r="J135" t="str">
-        <x:v>value</x:v>
-      </x:c>
-      <x:c r="K135"/>
-      <x:c r="L135" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="M135"/>
-      <x:c r="N135" t="str">
-        <x:v>数值；按比例为万分比增量</x:v>
-      </x:c>
-      <x:c r="O135"/>
-      <x:c r="P135"/>
     </x:row>
     <x:row r="136">
       <x:c r="A136"/>
       <x:c r="B136" t="str">
-        <x:v>AffixAimMod</x:v>
-      </x:c>
-      <x:c r="C136" t="str">
         <x:v>AffixMod</x:v>
       </x:c>
+      <x:c r="C136"/>
       <x:c r="D136"/>
       <x:c r="E136"/>
-      <x:c r="F136" t="str">
-        <x:v>修改_瞄准类型</x:v>
-      </x:c>
+      <x:c r="F136"/>
       <x:c r="G136" t="str">
-        <x:v>替换技能瞄准类型</x:v>
-      </x:c>
-      <x:c r="H136" t="str">
-        <x:v>a</x:v>
-      </x:c>
+        <x:v>词条的一次修改（多态基类）：公共字段是定位——目标位置 / 序号 / 效果限定 / 沿引用；子类是修改操作，各自只有自己那一段列</x:v>
+      </x:c>
+      <x:c r="H136"/>
       <x:c r="I136"/>
       <x:c r="J136" t="str">
-        <x:v>aim_kind</x:v>
+        <x:v>slot</x:v>
       </x:c>
       <x:c r="K136"/>
       <x:c r="L136" t="str">
-        <x:v>AimKind</x:v>
+        <x:v>AffixSlot</x:v>
       </x:c>
       <x:c r="M136"/>
-      <x:c r="N136" t="str">
-        <x:v>瞄准类型</x:v>
+      <x:c r="N136" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">【公共】目标位置：自身 / 主选择器 / 子选择器 / 效果 / 效果列表 / 新增项</x:t>
+        </x:is>
       </x:c>
       <x:c r="O136"/>
       <x:c r="P136"/>
     </x:row>
     <x:row r="137">
       <x:c r="A137"/>
-      <x:c r="B137" t="str">
-        <x:v>AffixSelectorParamMod</x:v>
-      </x:c>
-      <x:c r="C137" t="str">
-        <x:v>AffixMod</x:v>
-      </x:c>
+      <x:c r="B137"/>
+      <x:c r="C137"/>
       <x:c r="D137"/>
       <x:c r="E137"/>
-      <x:c r="F137" t="str">
-        <x:v>修改_选择器参数</x:v>
-      </x:c>
-      <x:c r="G137" t="str">
-        <x:v>修改选择器数值</x:v>
-      </x:c>
-      <x:c r="H137" t="str">
-        <x:v>a</x:v>
-      </x:c>
+      <x:c r="F137"/>
+      <x:c r="G137"/>
+      <x:c r="H137"/>
       <x:c r="I137"/>
       <x:c r="J137" t="str">
-        <x:v>selector</x:v>
+        <x:v>index</x:v>
       </x:c>
       <x:c r="K137"/>
       <x:c r="L137" t="str">
-        <x:v>AffixSelectorSlot</x:v>
+        <x:v>int</x:v>
       </x:c>
       <x:c r="M137"/>
-      <x:c r="N137" t="str">
-        <x:v>主选择器或子选择器</x:v>
+      <x:c r="N137" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">【公共】序号：位置为“效果”时填第几个效果（1 起），0=全部符合效果限定的效果；“新增项”填本条词条第几次追加；其余留空</x:t>
+        </x:is>
       </x:c>
       <x:c r="O137"/>
       <x:c r="P137"/>
@@ -3741,15 +3765,17 @@
       <x:c r="H138"/>
       <x:c r="I138"/>
       <x:c r="J138" t="str">
-        <x:v>param</x:v>
+        <x:v>filter</x:v>
       </x:c>
       <x:c r="K138"/>
       <x:c r="L138" t="str">
-        <x:v>AffixSelectorParam</x:v>
+        <x:v>AffixEffectType</x:v>
       </x:c>
       <x:c r="M138"/>
-      <x:c r="N138" t="str">
-        <x:v>选择器参数</x:v>
+      <x:c r="N138" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">【公共】效果限定：位置为“效果”且序号为 0 时按类型筛选；其余可留空</x:t>
+        </x:is>
       </x:c>
       <x:c r="O138"/>
       <x:c r="P138"/>
@@ -3765,15 +3791,17 @@
       <x:c r="H139"/>
       <x:c r="I139"/>
       <x:c r="J139" t="str">
-        <x:v>op</x:v>
+        <x:v>via</x:v>
       </x:c>
       <x:c r="K139"/>
       <x:c r="L139" t="str">
-        <x:v>AffixModifyOp</x:v>
+        <x:v>AffixVia</x:v>
       </x:c>
       <x:c r="M139"/>
-      <x:c r="N139" t="str">
-        <x:v>修改方式</x:v>
+      <x:c r="N139" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">【公共】沿引用：定位到的效果引用了状态 / 神通时，填“引用状态”或“调用神通”继续进入；不进入留空</x:t>
+        </x:is>
       </x:c>
       <x:c r="O139"/>
       <x:c r="P139"/>
@@ -3789,73 +3817,75 @@
       <x:c r="H140"/>
       <x:c r="I140"/>
       <x:c r="J140" t="str">
-        <x:v>value</x:v>
+        <x:v>via_slot</x:v>
       </x:c>
       <x:c r="K140"/>
       <x:c r="L140" t="str">
-        <x:v>float</x:v>
+        <x:v>AffixSlot</x:v>
       </x:c>
       <x:c r="M140"/>
-      <x:c r="N140" t="str">
-        <x:v>数值</x:v>
+      <x:c r="N140" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">【公共】引用内位置：沿引用后在被引用对象里的位置（自身 / 主选择器 / 效果…）</x:t>
+        </x:is>
       </x:c>
       <x:c r="O140"/>
       <x:c r="P140"/>
     </x:row>
     <x:row r="141">
       <x:c r="A141"/>
-      <x:c r="B141" t="str">
-        <x:v>AffixSelectorFilterMod</x:v>
-      </x:c>
-      <x:c r="C141" t="str">
-        <x:v>AffixMod</x:v>
-      </x:c>
+      <x:c r="B141"/>
+      <x:c r="C141"/>
       <x:c r="D141"/>
       <x:c r="E141"/>
-      <x:c r="F141" t="str">
-        <x:v>修改_选择器筛选</x:v>
-      </x:c>
-      <x:c r="G141" t="str">
-        <x:v>修改选择器筛选条件</x:v>
-      </x:c>
-      <x:c r="H141" t="str">
-        <x:v>a</x:v>
-      </x:c>
+      <x:c r="F141"/>
+      <x:c r="G141"/>
+      <x:c r="H141"/>
       <x:c r="I141"/>
       <x:c r="J141" t="str">
-        <x:v>selector</x:v>
+        <x:v>via_index</x:v>
       </x:c>
       <x:c r="K141"/>
       <x:c r="L141" t="str">
-        <x:v>AffixSelectorSlot</x:v>
+        <x:v>int</x:v>
       </x:c>
       <x:c r="M141"/>
-      <x:c r="N141" t="str">
-        <x:v>主选择器或子选择器</x:v>
+      <x:c r="N141" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">【公共】引用内序号：引用内位置为“效果”时的序号，规则同“序号”</x:t>
+        </x:is>
       </x:c>
       <x:c r="O141"/>
       <x:c r="P141"/>
     </x:row>
     <x:row r="142">
       <x:c r="A142"/>
-      <x:c r="B142"/>
-      <x:c r="C142"/>
+      <x:c r="B142" t="str">
+        <x:v>AffixAdjustMod</x:v>
+      </x:c>
+      <x:c r="C142" t="str">
+        <x:v>AffixMod</x:v>
+      </x:c>
       <x:c r="D142"/>
       <x:c r="E142"/>
-      <x:c r="F142"/>
-      <x:c r="G142"/>
+      <x:c r="F142" t="str">
+        <x:v>增减</x:v>
+      </x:c>
+      <x:c r="G142" t="str">
+        <x:v>对同一个参数做固定增减和/或按比例缩放，两列可以同时填（先加固定值，再按比例缩放）；不参与覆盖优先级争用</x:v>
+      </x:c>
       <x:c r="H142"/>
       <x:c r="I142"/>
       <x:c r="J142" t="str">
-        <x:v>target_faction</x:v>
+        <x:v>adj_param</x:v>
       </x:c>
       <x:c r="K142"/>
       <x:c r="L142" t="str">
-        <x:v>TargetFaction</x:v>
+        <x:v>AffixParam</x:v>
       </x:c>
       <x:c r="M142"/>
       <x:c r="N142" t="str">
-        <x:v>无=不改</x:v>
+        <x:v>【增减】修改项目：参数目录里的中文名</x:v>
       </x:c>
       <x:c r="O142"/>
       <x:c r="P142"/>
@@ -3871,15 +3901,15 @@
       <x:c r="H143"/>
       <x:c r="I143"/>
       <x:c r="J143" t="str">
-        <x:v>include_caster</x:v>
+        <x:v>adj_add</x:v>
       </x:c>
       <x:c r="K143"/>
       <x:c r="L143" t="str">
-        <x:v>bool?</x:v>
+        <x:v>int</x:v>
       </x:c>
       <x:c r="M143"/>
       <x:c r="N143" t="str">
-        <x:v>null=不改；true/false=修改，流式配置不可留空</x:v>
+        <x:v>【增减】固定增减值：按参数单位加减，可正可负；不改就留空</x:v>
       </x:c>
       <x:c r="O143"/>
       <x:c r="P143"/>
@@ -3895,15 +3925,15 @@
       <x:c r="H144"/>
       <x:c r="I144"/>
       <x:c r="J144" t="str">
-        <x:v>priority</x:v>
+        <x:v>adj_pct</x:v>
       </x:c>
       <x:c r="K144"/>
       <x:c r="L144" t="str">
-        <x:v>TargetPriority</x:v>
+        <x:v>int</x:v>
       </x:c>
       <x:c r="M144"/>
       <x:c r="N144" t="str">
-        <x:v>无=不改</x:v>
+        <x:v>【增减】按比例值：万分比增量，2000=+20%，-1000=-10%；不改就留空</x:v>
       </x:c>
       <x:c r="O144"/>
       <x:c r="P144"/>
@@ -3911,7 +3941,7 @@
     <x:row r="145">
       <x:c r="A145"/>
       <x:c r="B145" t="str">
-        <x:v>AffixReplaceSelectorMod</x:v>
+        <x:v>AffixSetMod</x:v>
       </x:c>
       <x:c r="C145" t="str">
         <x:v>AffixMod</x:v>
@@ -3919,25 +3949,23 @@
       <x:c r="D145"/>
       <x:c r="E145"/>
       <x:c r="F145" t="str">
-        <x:v>替换_选择器</x:v>
+        <x:v>设定</x:v>
       </x:c>
       <x:c r="G145" t="str">
-        <x:v>完整替换选择器，字段顺序与技能表一致</x:v>
-      </x:c>
-      <x:c r="H145" t="str">
-        <x:v>a</x:v>
-      </x:c>
+        <x:v>把参数设为指定值：数值填修改值，文本填文本值，选项只填对应的选项列</x:v>
+      </x:c>
+      <x:c r="H145"/>
       <x:c r="I145"/>
       <x:c r="J145" t="str">
-        <x:v>selector</x:v>
+        <x:v>set_param</x:v>
       </x:c>
       <x:c r="K145"/>
       <x:c r="L145" t="str">
-        <x:v>AffixSelectorSlot</x:v>
+        <x:v>AffixParam</x:v>
       </x:c>
       <x:c r="M145"/>
       <x:c r="N145" t="str">
-        <x:v>主选择器或子选择器</x:v>
+        <x:v>【设定】修改项目：数值 / 文本参数时填参数目录里的中文名；只设选项时留空</x:v>
       </x:c>
       <x:c r="O145"/>
       <x:c r="P145"/>
@@ -3953,49 +3981,39 @@
       <x:c r="H146"/>
       <x:c r="I146"/>
       <x:c r="J146" t="str">
-        <x:v>replacement</x:v>
+        <x:v>set_value</x:v>
       </x:c>
       <x:c r="K146"/>
       <x:c r="L146" t="str">
-        <x:v>SkillSelector</x:v>
+        <x:v>int</x:v>
       </x:c>
       <x:c r="M146"/>
       <x:c r="N146" t="str">
-        <x:v>新选择器：形状、阵营、数量、自身、优先级及形状参数</x:v>
+        <x:v>【设定】修改值：目标数值（是/否填 1/0，引用ID填行ID）</x:v>
       </x:c>
       <x:c r="O146"/>
       <x:c r="P146"/>
     </x:row>
     <x:row r="147">
       <x:c r="A147"/>
-      <x:c r="B147" t="str">
-        <x:v>AffixEffectParamMod</x:v>
-      </x:c>
-      <x:c r="C147" t="str">
-        <x:v>AffixMod</x:v>
-      </x:c>
+      <x:c r="B147"/>
+      <x:c r="C147"/>
       <x:c r="D147"/>
       <x:c r="E147"/>
-      <x:c r="F147" t="str">
-        <x:v>修改_效果参数</x:v>
-      </x:c>
-      <x:c r="G147" t="str">
-        <x:v>修改指定效果的参数</x:v>
-      </x:c>
-      <x:c r="H147" t="str">
-        <x:v>a</x:v>
-      </x:c>
+      <x:c r="F147"/>
+      <x:c r="G147"/>
+      <x:c r="H147"/>
       <x:c r="I147"/>
       <x:c r="J147" t="str">
-        <x:v>effect_slot</x:v>
+        <x:v>set_text</x:v>
       </x:c>
       <x:c r="K147"/>
       <x:c r="L147" t="str">
-        <x:v>int</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="M147"/>
       <x:c r="N147" t="str">
-        <x:v>1/2/3，0=全部同类型</x:v>
+        <x:v>【设定】文本值：动作名、资源路径这类文本参数</x:v>
       </x:c>
       <x:c r="O147"/>
       <x:c r="P147"/>
@@ -4011,15 +4029,15 @@
       <x:c r="H148"/>
       <x:c r="I148"/>
       <x:c r="J148" t="str">
-        <x:v>effect_type</x:v>
+        <x:v>set_aim</x:v>
       </x:c>
       <x:c r="K148"/>
       <x:c r="L148" t="str">
-        <x:v>AffixEffectType</x:v>
+        <x:v>AimKind?</x:v>
       </x:c>
       <x:c r="M148"/>
       <x:c r="N148" t="str">
-        <x:v>位置为0时指定类型，其余填无</x:v>
+        <x:v>【设定】瞄准类型：位置=自身(神通)</x:v>
       </x:c>
       <x:c r="O148"/>
       <x:c r="P148"/>
@@ -4035,15 +4053,15 @@
       <x:c r="H149"/>
       <x:c r="I149"/>
       <x:c r="J149" t="str">
-        <x:v>param</x:v>
+        <x:v>set_skill_class</x:v>
       </x:c>
       <x:c r="K149"/>
       <x:c r="L149" t="str">
-        <x:v>AffixEffectParam</x:v>
+        <x:v>ClassType?</x:v>
       </x:c>
       <x:c r="M149"/>
       <x:c r="N149" t="str">
-        <x:v>公共字段或类型参数1至13</x:v>
+        <x:v>【设定】生效系别：位置=自身(神通)，转换后按最终系别匹配</x:v>
       </x:c>
       <x:c r="O149"/>
       <x:c r="P149"/>
@@ -4059,15 +4077,15 @@
       <x:c r="H150"/>
       <x:c r="I150"/>
       <x:c r="J150" t="str">
-        <x:v>op</x:v>
+        <x:v>set_faction</x:v>
       </x:c>
       <x:c r="K150"/>
       <x:c r="L150" t="str">
-        <x:v>AffixModifyOp</x:v>
+        <x:v>TargetFaction?</x:v>
       </x:c>
       <x:c r="M150"/>
       <x:c r="N150" t="str">
-        <x:v>修改方式</x:v>
+        <x:v>【设定】目标阵营：位置=主选择器 / 子选择器 / 效果</x:v>
       </x:c>
       <x:c r="O150"/>
       <x:c r="P150"/>
@@ -4083,15 +4101,15 @@
       <x:c r="H151"/>
       <x:c r="I151"/>
       <x:c r="J151" t="str">
-        <x:v>value</x:v>
+        <x:v>set_priority</x:v>
       </x:c>
       <x:c r="K151"/>
       <x:c r="L151" t="str">
-        <x:v>float</x:v>
+        <x:v>TargetPriority?</x:v>
       </x:c>
       <x:c r="M151"/>
       <x:c r="N151" t="str">
-        <x:v>数值</x:v>
+        <x:v>【设定】目标优先级：位置=主选择器 / 子选择器</x:v>
       </x:c>
       <x:c r="O151"/>
       <x:c r="P151"/>
@@ -4107,49 +4125,39 @@
       <x:c r="H152"/>
       <x:c r="I152"/>
       <x:c r="J152" t="str">
-        <x:v>text_value</x:v>
+        <x:v>set_time_override</x:v>
       </x:c>
       <x:c r="K152"/>
       <x:c r="L152" t="str">
-        <x:v>string?</x:v>
+        <x:v>BuffTimeOverrideType?</x:v>
       </x:c>
       <x:c r="M152"/>
       <x:c r="N152" t="str">
-        <x:v>可空字符串参数值</x:v>
+        <x:v>【设定】时间覆盖方式：位置=自身(状态)</x:v>
       </x:c>
       <x:c r="O152"/>
       <x:c r="P152"/>
     </x:row>
     <x:row r="153">
       <x:c r="A153"/>
-      <x:c r="B153" t="str">
-        <x:v>AffixReplaceEffectMod</x:v>
-      </x:c>
-      <x:c r="C153" t="str">
-        <x:v>AffixMod</x:v>
-      </x:c>
+      <x:c r="B153"/>
+      <x:c r="C153"/>
       <x:c r="D153"/>
       <x:c r="E153"/>
-      <x:c r="F153" t="str">
-        <x:v>替换_效果</x:v>
-      </x:c>
-      <x:c r="G153" t="str">
-        <x:v>完整替换指定效果，效果列顺序与技能表一致</x:v>
-      </x:c>
-      <x:c r="H153" t="str">
-        <x:v>a</x:v>
-      </x:c>
+      <x:c r="F153"/>
+      <x:c r="G153"/>
+      <x:c r="H153"/>
       <x:c r="I153"/>
       <x:c r="J153" t="str">
-        <x:v>effect_slot</x:v>
+        <x:v>set_pile_type</x:v>
       </x:c>
       <x:c r="K153"/>
       <x:c r="L153" t="str">
-        <x:v>int</x:v>
+        <x:v>BuffOverrideType?</x:v>
       </x:c>
       <x:c r="M153"/>
       <x:c r="N153" t="str">
-        <x:v>效果位置1/2/3</x:v>
+        <x:v>【设定】层数叠加方式：位置=自身(状态)</x:v>
       </x:c>
       <x:c r="O153"/>
       <x:c r="P153"/>
@@ -4165,49 +4173,39 @@
       <x:c r="H154"/>
       <x:c r="I154"/>
       <x:c r="J154" t="str">
-        <x:v>replacement</x:v>
+        <x:v>set_attr_key</x:v>
       </x:c>
       <x:c r="K154"/>
       <x:c r="L154" t="str">
-        <x:v>SkillEffect</x:v>
+        <x:v>AttrKey?</x:v>
       </x:c>
       <x:c r="M154"/>
       <x:c r="N154" t="str">
-        <x:v>新效果完整配置</x:v>
+        <x:v>【设定】属性修正类型：位置=效果，限定 属性修正</x:v>
       </x:c>
       <x:c r="O154"/>
       <x:c r="P154"/>
     </x:row>
     <x:row r="155">
       <x:c r="A155"/>
-      <x:c r="B155" t="str">
-        <x:v>AffixAppendEffectMod</x:v>
-      </x:c>
-      <x:c r="C155" t="str">
-        <x:v>AffixMod</x:v>
-      </x:c>
+      <x:c r="B155"/>
+      <x:c r="C155"/>
       <x:c r="D155"/>
       <x:c r="E155"/>
-      <x:c r="F155" t="str">
-        <x:v>追加_效果</x:v>
-      </x:c>
-      <x:c r="G155" t="str">
-        <x:v>追加完整效果</x:v>
-      </x:c>
-      <x:c r="H155" t="str">
-        <x:v>a</x:v>
-      </x:c>
+      <x:c r="F155"/>
+      <x:c r="G155"/>
+      <x:c r="H155"/>
       <x:c r="I155"/>
       <x:c r="J155" t="str">
-        <x:v>effect</x:v>
+        <x:v>set_control</x:v>
       </x:c>
       <x:c r="K155"/>
       <x:c r="L155" t="str">
-        <x:v>SkillEffect</x:v>
+        <x:v>BuffEffectTag?</x:v>
       </x:c>
       <x:c r="M155"/>
       <x:c r="N155" t="str">
-        <x:v>追加的完整效果配置</x:v>
+        <x:v>【设定】控制类型：位置=效果，限定 控制</x:v>
       </x:c>
       <x:c r="O155"/>
       <x:c r="P155"/>
@@ -4215,7 +4213,7 @@
     <x:row r="156">
       <x:c r="A156"/>
       <x:c r="B156" t="str">
-        <x:v>AffixRemoveEffectMod</x:v>
+        <x:v>AffixReplaceMod</x:v>
       </x:c>
       <x:c r="C156" t="str">
         <x:v>AffixMod</x:v>
@@ -4223,17 +4221,15 @@
       <x:c r="D156"/>
       <x:c r="E156"/>
       <x:c r="F156" t="str">
-        <x:v>移除_效果</x:v>
+        <x:v>替换</x:v>
       </x:c>
       <x:c r="G156" t="str">
-        <x:v>移除指定效果</x:v>
-      </x:c>
-      <x:c r="H156" t="str">
-        <x:v>a</x:v>
-      </x:c>
+        <x:v>用模板行里选定的选择器 / 效果整项替换目标位置</x:v>
+      </x:c>
+      <x:c r="H156"/>
       <x:c r="I156"/>
       <x:c r="J156" t="str">
-        <x:v>effect_slot</x:v>
+        <x:v>replace_id</x:v>
       </x:c>
       <x:c r="K156"/>
       <x:c r="L156" t="str">
@@ -4241,41 +4237,31 @@
       </x:c>
       <x:c r="M156"/>
       <x:c r="N156" t="str">
-        <x:v>效果位置1/2/3</x:v>
+        <x:v>【替换】模板行ID：目标是神通内容填神通等级行ID，目标是状态内容填状态ID</x:v>
       </x:c>
       <x:c r="O156"/>
       <x:c r="P156"/>
     </x:row>
     <x:row r="157">
       <x:c r="A157"/>
-      <x:c r="B157" t="str">
-        <x:v>AffixResourceMod</x:v>
-      </x:c>
-      <x:c r="C157" t="str">
-        <x:v>AffixMod</x:v>
-      </x:c>
+      <x:c r="B157"/>
+      <x:c r="C157"/>
       <x:c r="D157"/>
       <x:c r="E157"/>
-      <x:c r="F157" t="str">
-        <x:v>修改_表现资源</x:v>
-      </x:c>
-      <x:c r="G157" t="str">
-        <x:v>替换技能表现资源</x:v>
-      </x:c>
-      <x:c r="H157" t="str">
-        <x:v>a</x:v>
-      </x:c>
+      <x:c r="F157"/>
+      <x:c r="G157"/>
+      <x:c r="H157"/>
       <x:c r="I157"/>
       <x:c r="J157" t="str">
-        <x:v>param</x:v>
+        <x:v>replace_slot</x:v>
       </x:c>
       <x:c r="K157"/>
       <x:c r="L157" t="str">
-        <x:v>AffixResourceParam</x:v>
+        <x:v>AffixSlot</x:v>
       </x:c>
       <x:c r="M157"/>
       <x:c r="N157" t="str">
-        <x:v>表现资源字段</x:v>
+        <x:v>【替换】模板位置：模板行里取哪一块（主选择器 / 子选择器 / 效果）</x:v>
       </x:c>
       <x:c r="O157"/>
       <x:c r="P157"/>
@@ -4291,18 +4277,1231 @@
       <x:c r="H158"/>
       <x:c r="I158"/>
       <x:c r="J158" t="str">
-        <x:v>value</x:v>
+        <x:v>replace_index</x:v>
       </x:c>
       <x:c r="K158"/>
       <x:c r="L158" t="str">
-        <x:v>string</x:v>
+        <x:v>int</x:v>
       </x:c>
       <x:c r="M158"/>
       <x:c r="N158" t="str">
-        <x:v>动作名、资源路径或ID</x:v>
+        <x:v>【替换】模板序号：模板位置为“效果”时取第几个效果（1 起）</x:v>
       </x:c>
       <x:c r="O158"/>
       <x:c r="P158"/>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159"/>
+      <x:c r="B159" t="str">
+        <x:v>AffixAppendMod</x:v>
+      </x:c>
+      <x:c r="C159" t="str">
+        <x:v>AffixMod</x:v>
+      </x:c>
+      <x:c r="D159"/>
+      <x:c r="E159"/>
+      <x:c r="F159" t="str">
+        <x:v>追加</x:v>
+      </x:c>
+      <x:c r="G159" t="str">
+        <x:v>把模板行里选定的效果整项加到目标效果列表末尾</x:v>
+      </x:c>
+      <x:c r="H159"/>
+      <x:c r="I159"/>
+      <x:c r="J159" t="str">
+        <x:v>append_id</x:v>
+      </x:c>
+      <x:c r="K159"/>
+      <x:c r="L159" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="M159"/>
+      <x:c r="N159" t="str">
+        <x:v>【追加】模板行ID：目标是神通填神通等级行ID，目标是状态填状态ID</x:v>
+      </x:c>
+      <x:c r="O159"/>
+      <x:c r="P159"/>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160"/>
+      <x:c r="B160"/>
+      <x:c r="C160"/>
+      <x:c r="D160"/>
+      <x:c r="E160"/>
+      <x:c r="F160"/>
+      <x:c r="G160"/>
+      <x:c r="H160"/>
+      <x:c r="I160"/>
+      <x:c r="J160" t="str">
+        <x:v>append_slot</x:v>
+      </x:c>
+      <x:c r="K160"/>
+      <x:c r="L160" t="str">
+        <x:v>AffixSlot</x:v>
+      </x:c>
+      <x:c r="M160"/>
+      <x:c r="N160" t="str">
+        <x:v>【追加】模板位置：模板行里取哪一块（效果）</x:v>
+      </x:c>
+      <x:c r="O160"/>
+      <x:c r="P160"/>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161"/>
+      <x:c r="B161"/>
+      <x:c r="C161"/>
+      <x:c r="D161"/>
+      <x:c r="E161"/>
+      <x:c r="F161"/>
+      <x:c r="G161"/>
+      <x:c r="H161"/>
+      <x:c r="I161"/>
+      <x:c r="J161" t="str">
+        <x:v>append_index</x:v>
+      </x:c>
+      <x:c r="K161"/>
+      <x:c r="L161" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="M161"/>
+      <x:c r="N161" t="str">
+        <x:v>【追加】模板序号：取模板行第几个效果（1 起）</x:v>
+      </x:c>
+      <x:c r="O161"/>
+      <x:c r="P161"/>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162"/>
+      <x:c r="B162" t="str">
+        <x:v>AffixRemoveMod</x:v>
+      </x:c>
+      <x:c r="C162" t="str">
+        <x:v>AffixMod</x:v>
+      </x:c>
+      <x:c r="D162"/>
+      <x:c r="E162"/>
+      <x:c r="F162" t="str">
+        <x:v>移除</x:v>
+      </x:c>
+      <x:c r="G162" t="str">
+        <x:v>把目标位置的效果移出有效组合，其余效果编号不重排；没有自己的列</x:v>
+      </x:c>
+      <x:c r="H162"/>
+      <x:c r="I162"/>
+      <x:c r="J162"/>
+      <x:c r="K162"/>
+      <x:c r="L162"/>
+      <x:c r="M162"/>
+      <x:c r="N162"/>
+      <x:c r="O162"/>
+      <x:c r="P162"/>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163"/>
+      <x:c r="B163" t="str">
+        <x:v>BreakRateMaterial</x:v>
+      </x:c>
+      <x:c r="C163"/>
+      <x:c r="D163"/>
+      <x:c r="E163"/>
+      <x:c r="F163"/>
+      <x:c r="G163" t="str">
+        <x:v>成功率加成材料</x:v>
+      </x:c>
+      <x:c r="H163"/>
+      <x:c r="I163"/>
+      <x:c r="J163" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="K163"/>
+      <x:c r="L163" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="M163"/>
+      <x:c r="N163" t="str">
+        <x:v>加成材料物品ID（当前为突破丹）</x:v>
+      </x:c>
+      <x:c r="O163"/>
+      <x:c r="P163"/>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164"/>
+      <x:c r="B164"/>
+      <x:c r="C164"/>
+      <x:c r="D164"/>
+      <x:c r="E164"/>
+      <x:c r="F164"/>
+      <x:c r="G164"/>
+      <x:c r="H164"/>
+      <x:c r="I164"/>
+      <x:c r="J164" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="K164"/>
+      <x:c r="L164" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="M164"/>
+      <x:c r="N164" t="str">
+        <x:v>投入数量</x:v>
+      </x:c>
+      <x:c r="O164"/>
+      <x:c r="P164"/>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165"/>
+      <x:c r="B165"/>
+      <x:c r="C165"/>
+      <x:c r="D165"/>
+      <x:c r="E165"/>
+      <x:c r="F165"/>
+      <x:c r="G165"/>
+      <x:c r="H165"/>
+      <x:c r="I165"/>
+      <x:c r="J165" t="str">
+        <x:v>rate</x:v>
+      </x:c>
+      <x:c r="K165"/>
+      <x:c r="L165" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="M165"/>
+      <x:c r="N165" t="str">
+        <x:v>增加成功率（万分比，与 base_success_rate 同口径）</x:v>
+      </x:c>
+      <x:c r="O165"/>
+      <x:c r="P165"/>
+    </x:row>
+    <x:row r="166">
+      <x:c r="B166" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PillClearToxinEffect</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C166" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PillEffect</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F166" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">清丹毒</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G166" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">丹药药效_清丹毒：清除丹方五味对应池的绝对杂质，再刷新丹毒；duration=0立即清除，正数为药力持续时间，到期不返还已清杂质</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H166" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">a</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J166" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">value</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L166" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N166" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">总清除量（绝对杂质，正整数）；服用时按药效倍率折算，最多清至0；duration&gt;0时在该现实秒数内逐步清除总量</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="167">
+      <x:c r="B167" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PillReduceWeaknessSecondsEffect</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C167" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PillEffect</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F167" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">减虚弱秒数</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G167" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">丹药药效_减虚弱秒数：一次性扣减突破失败虚弱的剩余时间，最多扣至0并解除；不修改虚弱属性</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H167" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">a</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J167" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">value</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L167" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N167" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">基础扣减现实秒数（正整数）；按服用时药效倍率折算，丹方duration填0</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="168">
+      <x:c r="B168" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PillReduceWeaknessRatioEffect</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C168" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PillEffect</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F168" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">减虚弱万分比</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G168" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">丹药药效_减虚弱万分比：按角色本级基础虚弱时间计算，一次性扣减剩余时间，最多扣至0并解除</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H168" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">a</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J168" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">value</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L168" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N168" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">本级realm_config.fail_weakness的万分比（1至10000，100=1%）；不按剩余时间计算；扣减量按服用时药效倍率折算，丹方duration填0</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="169">
+      <x:c r="B169" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PillAddCultEffect</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C169" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PillEffect</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F169" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">加修为</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G169" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">丹药药效_加修为：直接增加累计修为，允许超过突破门槛计入溢出、不自动升级；duration=0 立即一次性加入，正数为药力持续秒数，在该时间内线性释放总量，不打坐、离线照算</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H169" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">a</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J169" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">value</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L169" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N169" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">基础修为总量（单位：修为点，正整数）；服用时按药效倍率折算后向下取整</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="170">
+      <x:c r="B170" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ItemCount</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G170" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">物品数量</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J170" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">item_id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L170" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N170" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">物品ID</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="171">
+      <x:c r="J171" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">count</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L171" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N171" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">数量</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="172">
+      <x:c r="B172" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CurrencyAmount</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G172" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">货币数量</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J172" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">money_id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L172" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CurrencyType</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N172" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">币种</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="173">
+      <x:c r="J173" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">amount</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L173" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">long</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N173" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">数量</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="174">
+      <x:c r="B174" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">QuestCond</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G174" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">任务条件（同一组内 AND）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J174" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">pred</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L174" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">QuestPred</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N174" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">谓词</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="175">
+      <x:c r="J175" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">a</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L175" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N175" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">参数a（含义由 pred 决定）</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="176">
+      <x:c r="J176" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">b</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L176" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N176" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">参数b（用不到填 0）</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="177">
+      <x:c r="B177" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">QuestObjective</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G177" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">任务目标</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J177" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">oid</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L177" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N177" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">目标序号：步骤内唯一且稳定（1、2、3…），存档按它记进度，不按数组下标</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="178">
+      <x:c r="J178" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">kind</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L178" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">QuestObjectiveKind</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N178" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">目标类型</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="179">
+      <x:c r="J179" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">target</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L179" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N179" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">主参数（含义由 kind 决定）</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="180">
+      <x:c r="J180" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">param</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L180" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N180" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">副参数（含义由 kind 决定，用不到填 0）</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="181">
+      <x:c r="J181" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">count</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L181" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N181" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">需要的数量 / 阈值（事件类默认 1）</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="182">
+      <x:c r="J182" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">kill_scope</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L182" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">KillScope</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N182" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">击杀计数范围：只 KillMonster 读；用到的槽也要填，其他类型填 同图</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="183">
+      <x:c r="J183" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">count_mode</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L183" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CountMode</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N183" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">计数起算：事件类目标决定从哪一刻开始计数，持有物品 / 持有货币决定是否扣掉起算时已有的量；阈值类目标不受影响；事件类目标不能填 可回溯；用到的槽也要填</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="184">
+      <x:c r="B184" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">QuestGrant</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G184" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">步骤授予：步骤完成时同闭包授予</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J184" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">type</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L184" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">QuestGrantType</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N184" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">授予类型</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="185">
+      <x:c r="J185" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L185" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N185" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">对象ID（含义由 type 决定）</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="186">
+      <x:c r="J186" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">count</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L186" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N186" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">数量</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="187">
+      <x:c r="B187" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">QuestStepAction</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G187" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">步骤表现动作（只客户端读）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H187" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">c</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J187" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">action_id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L187" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N187" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">动作ID：步骤内唯一且稳定，表现恢复按它去重</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="188">
+      <x:c r="J188" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">kind</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L188" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">QuestStepActionKind</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N188" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">动作类型</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="189">
+      <x:c r="J189" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">once</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L189" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">bool</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N189" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">一次性：true=同一步骤激活轮次只执行一次（传送必须 true）；false=每次恢复都重放</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="190">
+      <x:c r="J190" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">target</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L190" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N190" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">主参数（含义由 kind 决定）</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="191">
+      <x:c r="J191" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">param</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L191" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N191" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">副参数（用不到填 0）</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="192">
+      <x:c r="B192" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">AffixTarget</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G192" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">词条作用对象（多态基类）：系别 / 神通 / 状态选一个，子类各自只有自己那一列</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="193">
+      <x:c r="B193" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">AffixClassTarget</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C193" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">AffixTarget</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F193" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">系别</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G193" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">按系别作用：命中该系别内全部神通（五行覆盖金木水火土各行）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J193" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">skill_class</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L193" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ClassType</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N193" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">【系别】作用系别；不能填“无”</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="194">
+      <x:c r="B194" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">AffixSkillTarget</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C194" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">AffixTarget</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F194" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">神通</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G194" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">按神通作用：命中该神通识别ID的各等级行</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J194" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">skill_identify_id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L194" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N194" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">【神通】作用神通识别ID；填正数</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="195">
+      <x:c r="B195" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">AffixBuffTarget</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C195" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">AffixTarget</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F195" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">状态</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G195" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">按状态作用：命中该状态识别ID的各等级行，角色施加的该状态各调用来源都生效</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J195" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">buff_identify_id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L195" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">string</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N195" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">【状态】作用状态识别ID；不能留空</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="196">
+      <x:c r="B196" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ActivitySpec</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G196" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">日常活动（多态基类）：巡逻 / 游走 / 跟随 / 漂移 / 绕飞选一个，子类各自只有自己那一段列；驻留不建行（引用填 0）</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="197">
+      <x:c r="B197" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PatrolSpec</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C197" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ActivitySpec</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F197" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">巡逻</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G197" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">沿路点巡逻，到点停留，接战打断后回打断处续走</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J197" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">waypoints</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L197" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">array,int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N197" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">【巡逻】路点：region_config 区域ID，取矩形中心；至少两个</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="198">
+      <x:c r="J198" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">patrol_mode</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L198" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PatrolMode</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N198" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">【巡逻】巡逻方式：循环 / 往返</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="199">
+      <x:c r="J199" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">patrol_wait_ms</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L199" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N199" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">【巡逻】每路点停留(ms)：0=到点即走</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="200">
+      <x:c r="J200" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">patrol_timeout_ms</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L200" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N200" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">【巡逻】单段超时(ms)：走不到视为不可达、跳下一路点；0=不超时</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="201">
+      <x:c r="B201" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">WanderSpec</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C201" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ActivitySpec</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F201" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">游走</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G201" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">在区域内随机游走：以当前位置为起点摇落点、越界折回区域内，到点停留再走</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J201" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">wander_area</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L201" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N201" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">【游走】游走区域：region_config 区域ID</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="202">
+      <x:c r="J202" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">wander_wait_ms</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L202" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N202" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">【游走】每个落点停留(ms)：0=到点即走</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="203">
+      <x:c r="J203" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">wander_timeout_ms</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L203" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N203" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">【游走】单段超时(ms)：必填(&gt;0)，随机落点可能走不到，超时即重摇</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="204">
+      <x:c r="B204" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">FollowSpec</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C204" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ActivitySpec</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F204" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">跟随</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G204" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">跟着主人走：离主人超过跟随距离就追上去，进入就停；只给从属实体用</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J204" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">follow_range</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L204" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N204" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">【跟随】跟随距离(码)</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="205">
+      <x:c r="B205" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">DriftSpec</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C205" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ActivitySpec</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F205" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">漂移</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G205" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">沿生成朝向直线推进、不停；速度取移动速度属性（火蛇、推进火墙）；没有自己的列</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="206">
+      <x:c r="B206" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">OrbitSpec</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C206" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ActivitySpec</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F206" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">绕飞</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G206" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">绕着主人实时位置匀速转圈（法宝的场上表现）；每 tick 直接落点、不走寻路，只给不可选中、不可受击的单位用</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J206" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">orbit_radius</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L206" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N206" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">【绕飞】绕飞半径(码)：0=贴着主人不偏移</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="207">
+      <x:c r="J207" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">orbit_period_ms</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L207" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N207" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">【绕飞】一圈时长(ms)：必填正数</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="208">
+      <x:c r="J208" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">orbit_height</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L208" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N208" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">【绕飞】飞行高度(码)：0=贴地</x:t>
+        </x:is>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/配置表格/__beans__.xlsx
+++ b/配置表格/__beans__.xlsx
@@ -364,7 +364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P215"/>
+  <dimension ref="A1:P229"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="20.6640625" customWidth="1" style="8" min="2" max="4"/>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="N209" s="7" t="inlineStr">
         <is>
-          <t>驱散分类：减益=净化自己，增益=驱除敌对目标；无/中性非法。目标阵营另由 target_faction 筛选，不自动改目标。</t>
+          <t xml:space="preserve">驱散分类：减益=净化自己或友方，增益=驱除敌对目标；无/中性非法。目标阵营另由 target_faction 筛选，不自动改目标。</t>
         </is>
       </c>
     </row>
@@ -6031,6 +6031,394 @@
         </is>
       </c>
     </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="216">
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>PillAttrPercentEffect</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>PillEffect</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>加属性万分比</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>按基数增加指定属性的万分比贡献；duration须为正，value=100表示1%；不新增属性键。</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>attr</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>AttrKey</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>目标属性／触发属性，使用原字典键</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="217">
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>万分比数值，100=1%；服用时先按药效倍率缩放，不能当固定点数</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="218">
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>PillRestoreResourceEffect</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>PillEffect</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>立即回复万分比</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>服丹成功后立即回复生命或灵力上限的万分比；attr只允许生命值/灵力值；duration填0；必须有防重复消费身份。</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>attr</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>AttrKey</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>目标属性／触发属性，使用原字典键</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="219">
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>万分比数值，100=1%；服用时先按药效倍率缩放，不能当固定点数</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="220">
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>PillRecoveryRateEffect</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>PillEffect</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>回复率万分比</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>按35至40指定每秒/击中/受击触发，回复本人生命或灵力上限的value万分比；duration须为正；不足1点的部分用整数余数累计。</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>attr</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>AttrKey</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>目标属性／触发属性，使用原字典键</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="221">
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>万分比数值，100=1%；服用时先按药效倍率缩放，不能当固定点数</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SkillSeekEliteEffect</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SkillEffect</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">技能效果_寻踪传送</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">distance</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">传送到当前场景最近精英或首领附近的安全落点；与目标间隔(码)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="B223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SkillRandomTeleportEffect</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SkillEffect</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">技能效果_随机挪移</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">distance</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当前场景内随机安全传送的最大距离(码)，必须为正。</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="B224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SkillRevealEliteEffect</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SkillEffect</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">技能效果_精英标记</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duration</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在小地图标记当前场景精英或首领的持续时间(ms)，必须为正。</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SkillDamageComponent</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同一命中的独立伤害分量</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">effect_index</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">所属伤害效果序号，从1开始；必须指向本技能的伤害效果。</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="J226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">skill_class</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ClassType?</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">伤害分量分类；空=继承根技能最终分类，显式无(0)=无元素，毒=21。</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="J227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">damage_type</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DamageType</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">伤害攻防通道；0=继承原伤害效果，其余使用现有合法伤害类型。</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="J228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coefficient</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">本分量独立伤害系数（万分比），替代原效果系数，不是比例拆分。</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="J229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flat</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">本分量自身固定伤害（整数），替代原效果固定伤害。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>
